--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7524,7 +7524,7 @@
         <v>125656453</v>
       </c>
       <c r="B60" t="n">
-        <v>58063</v>
+        <v>58066</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>131431280</v>
       </c>
       <c r="B61" t="n">
-        <v>75285</v>
+        <v>75288</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>131431278</v>
       </c>
       <c r="B62" t="n">
-        <v>91895</v>
+        <v>91898</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7524,7 +7524,7 @@
         <v>125656453</v>
       </c>
       <c r="B60" t="n">
-        <v>58066</v>
+        <v>58071</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>131431280</v>
       </c>
       <c r="B61" t="n">
-        <v>75288</v>
+        <v>75293</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>131431278</v>
       </c>
       <c r="B62" t="n">
-        <v>91898</v>
+        <v>91903</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7524,7 +7524,7 @@
         <v>125656453</v>
       </c>
       <c r="B60" t="n">
-        <v>58071</v>
+        <v>58073</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7840,6 +7840,1622 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132218114</v>
+      </c>
+      <c r="B63" t="n">
+        <v>84096</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1444</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Scharlakansvårskål agg.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcoscypha coccinea s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Borg, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>707052</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6635913</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132218069</v>
+      </c>
+      <c r="B64" t="n">
+        <v>97919</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Borg, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>707184</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6635847</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132214935</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92272</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ekalund, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>707044</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6635846</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132216358</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fisingsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>707052</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6635680</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132214236</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80606</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ekalund, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>706939</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6635897</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132214790</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91905</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Ekalund, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>707028</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6635854</v>
+      </c>
+      <c r="S68" t="n">
+        <v>15</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132216648</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91869</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fisingsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>707065</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6635643</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132227423</v>
+      </c>
+      <c r="B70" t="n">
+        <v>96362</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Östra Eka, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>707098</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6635735</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132222629</v>
+      </c>
+      <c r="B71" t="n">
+        <v>106178</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Östra Eka SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>707139</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6635834</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>C:a 10 exemplar.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132215849</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99077</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fisingsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>707074</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6635682</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132222660</v>
+      </c>
+      <c r="B73" t="n">
+        <v>106178</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Östra Eka SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>707127</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6635639</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132227426</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99077</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Östra Eka, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>707352</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6635802</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132227420</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80341</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Östra Eka, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>707005</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6635885</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>132216402</v>
+      </c>
+      <c r="B76" t="n">
+        <v>107543</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fisingsberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>707053</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6635668</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>132217832</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Borg, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>707382</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6635863</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>132227427</v>
+      </c>
+      <c r="B78" t="n">
+        <v>92579</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>757</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Apelsinticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hapalopilus aurantiacus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Östra Eka, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>707230</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6635950</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8342,48 +8342,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132214790</v>
+        <v>132216648</v>
       </c>
       <c r="B68" t="n">
-        <v>91905</v>
+        <v>91869</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5321</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707028</v>
+        <v>707065</v>
       </c>
       <c r="R68" t="n">
-        <v>6635854</v>
+        <v>6635643</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8439,48 +8439,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132216648</v>
+        <v>132214790</v>
       </c>
       <c r="B69" t="n">
-        <v>91869</v>
+        <v>91905</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707065</v>
+        <v>707028</v>
       </c>
       <c r="R69" t="n">
-        <v>6635643</v>
+        <v>6635854</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B73" t="n">
-        <v>106178</v>
+        <v>99077</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,57 +8856,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R73" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8938,40 +8918,34 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B74" t="n">
-        <v>99077</v>
+        <v>106178</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8979,37 +8953,57 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R74" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9041,24 +9035,30 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9456,6 +9456,1003 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>132243950</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99077</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>707098</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6635691</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>132243953</v>
+      </c>
+      <c r="B80" t="n">
+        <v>58286</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>707009</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6635864</v>
+      </c>
+      <c r="S80" t="n">
+        <v>100</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>132243956</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79786</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1026</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ädellav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Megalaria grossa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Pers. ex Nyl.) Hafellner</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>707009</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6635864</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>132243957</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80606</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>706941</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6635897</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På en klen aspgren på en stor asplåga.</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Dead branch  # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>132243945</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57911</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>707094</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6635643</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132243949</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106139</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>340</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>707078</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6635703</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Blockig, gles blandskog</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132243955</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80341</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>707009</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6635864</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>132243952</v>
+      </c>
+      <c r="B86" t="n">
+        <v>58456</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>707009</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6635864</v>
+      </c>
+      <c r="S86" t="n">
+        <v>100</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8342,48 +8342,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132216648</v>
+        <v>132214790</v>
       </c>
       <c r="B68" t="n">
-        <v>91869</v>
+        <v>91905</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707065</v>
+        <v>707028</v>
       </c>
       <c r="R68" t="n">
-        <v>6635643</v>
+        <v>6635854</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8439,48 +8439,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132214790</v>
+        <v>132216648</v>
       </c>
       <c r="B69" t="n">
-        <v>91905</v>
+        <v>91869</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707028</v>
+        <v>707065</v>
       </c>
       <c r="R69" t="n">
-        <v>6635854</v>
+        <v>6635643</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B73" t="n">
-        <v>99077</v>
+        <v>106178</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,37 +8856,57 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R73" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8918,34 +8938,40 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B74" t="n">
-        <v>106178</v>
+        <v>99077</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,57 +8979,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R74" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9035,30 +9041,24 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9259,48 +9259,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132217832</v>
+        <v>132227427</v>
       </c>
       <c r="B77" t="n">
-        <v>91811</v>
+        <v>92579</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707382</v>
+        <v>707230</v>
       </c>
       <c r="R77" t="n">
-        <v>6635863</v>
+        <v>6635950</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,6 +9330,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9344,60 +9349,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132227427</v>
+        <v>132217832</v>
       </c>
       <c r="B78" t="n">
-        <v>92579</v>
+        <v>91811</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707230</v>
+        <v>707382</v>
       </c>
       <c r="R78" t="n">
-        <v>6635950</v>
+        <v>6635863</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,11 +9432,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,12 +9446,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9817,32 +9817,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B82" t="n">
-        <v>80606</v>
+        <v>57911</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9850,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R82" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9900,7 +9910,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9909,7 +9919,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9920,22 +9929,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9953,42 +9957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B83" t="n">
-        <v>57911</v>
+        <v>80606</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9996,10 +9990,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R83" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10046,7 +10040,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10055,6 +10049,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10065,17 +10060,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7845,7 +7845,7 @@
         <v>132218114</v>
       </c>
       <c r="B63" t="n">
-        <v>84135</v>
+        <v>84137</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>132218069</v>
       </c>
       <c r="B64" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>132214935</v>
       </c>
       <c r="B65" t="n">
-        <v>92313</v>
+        <v>92316</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8253,7 +8253,7 @@
         <v>132214236</v>
       </c>
       <c r="B67" t="n">
-        <v>80645</v>
+        <v>80647</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8335,55 +8335,55 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132216648</v>
+        <v>132214790</v>
       </c>
       <c r="B68" t="n">
-        <v>91910</v>
+        <v>91949</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707065</v>
+        <v>707028</v>
       </c>
       <c r="R68" t="n">
-        <v>6635643</v>
+        <v>6635854</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>132227423</v>
       </c>
       <c r="B69" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8536,48 +8536,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132214790</v>
+        <v>132216648</v>
       </c>
       <c r="B70" t="n">
-        <v>91946</v>
+        <v>91913</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707028</v>
+        <v>707065</v>
       </c>
       <c r="R70" t="n">
-        <v>6635854</v>
+        <v>6635643</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>132222629</v>
       </c>
       <c r="B71" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>132215849</v>
       </c>
       <c r="B72" t="n">
-        <v>99118</v>
+        <v>99121</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>106222</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,37 +8856,57 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R73" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8918,34 +8938,40 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B74" t="n">
-        <v>106219</v>
+        <v>99121</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,57 +8979,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R74" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9035,30 +9041,24 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9068,7 +9068,7 @@
         <v>132227420</v>
       </c>
       <c r="B75" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>132216402</v>
       </c>
       <c r="B76" t="n">
-        <v>107584</v>
+        <v>107587</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9252,55 +9252,55 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132217832</v>
+        <v>132227427</v>
       </c>
       <c r="B77" t="n">
-        <v>91852</v>
+        <v>92623</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707382</v>
+        <v>707230</v>
       </c>
       <c r="R77" t="n">
-        <v>6635863</v>
+        <v>6635950</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,6 +9330,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9344,60 +9349,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132227427</v>
+        <v>132217832</v>
       </c>
       <c r="B78" t="n">
-        <v>92620</v>
+        <v>91855</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707230</v>
+        <v>707382</v>
       </c>
       <c r="R78" t="n">
-        <v>6635950</v>
+        <v>6635863</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,11 +9432,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,12 +9446,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9461,7 +9461,7 @@
         <v>132243950</v>
       </c>
       <c r="B79" t="n">
-        <v>99118</v>
+        <v>99121</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9587,7 +9587,7 @@
         <v>132243953</v>
       </c>
       <c r="B80" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9708,7 +9708,7 @@
         <v>132243956</v>
       </c>
       <c r="B81" t="n">
-        <v>79825</v>
+        <v>79827</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9810,39 +9810,49 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B82" t="n">
-        <v>80645</v>
+        <v>57945</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9850,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R82" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9900,7 +9910,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9909,7 +9919,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9920,22 +9929,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9946,49 +9950,39 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B83" t="n">
-        <v>57945</v>
+        <v>80647</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9996,10 +9990,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R83" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10046,7 +10040,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10055,6 +10049,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10065,17 +10060,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106180</v>
+        <v>106183</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10225,7 +10225,7 @@
         <v>132243955</v>
       </c>
       <c r="B85" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10337,7 +10337,7 @@
         <v>132243952</v>
       </c>
       <c r="B86" t="n">
-        <v>58490</v>
+        <v>58492</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8342,10 +8342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132214790</v>
+        <v>132227423</v>
       </c>
       <c r="B68" t="n">
-        <v>91949</v>
+        <v>96406</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5321</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707028</v>
+        <v>707098</v>
       </c>
       <c r="R68" t="n">
-        <v>6635854</v>
+        <v>6635735</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8427,57 +8427,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132227423</v>
+        <v>132216648</v>
       </c>
       <c r="B69" t="n">
-        <v>96406</v>
+        <v>91913</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707098</v>
+        <v>707065</v>
       </c>
       <c r="R69" t="n">
-        <v>6635735</v>
+        <v>6635643</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8524,60 +8524,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132216648</v>
+        <v>132214790</v>
       </c>
       <c r="B70" t="n">
-        <v>91913</v>
+        <v>91949</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707065</v>
+        <v>707028</v>
       </c>
       <c r="R70" t="n">
-        <v>6635643</v>
+        <v>6635854</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8342,10 +8342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132227423</v>
+        <v>132214790</v>
       </c>
       <c r="B68" t="n">
-        <v>96406</v>
+        <v>91949</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>5321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707098</v>
+        <v>707028</v>
       </c>
       <c r="R68" t="n">
-        <v>6635735</v>
+        <v>6635854</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8427,57 +8427,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132216648</v>
+        <v>132227423</v>
       </c>
       <c r="B69" t="n">
-        <v>91913</v>
+        <v>96406</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707065</v>
+        <v>707098</v>
       </c>
       <c r="R69" t="n">
-        <v>6635643</v>
+        <v>6635735</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8524,60 +8524,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132214790</v>
+        <v>132216648</v>
       </c>
       <c r="B70" t="n">
-        <v>91949</v>
+        <v>91913</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707028</v>
+        <v>707065</v>
       </c>
       <c r="R70" t="n">
-        <v>6635854</v>
+        <v>6635643</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8342,10 +8342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132214790</v>
+        <v>132227423</v>
       </c>
       <c r="B68" t="n">
-        <v>91949</v>
+        <v>96406</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5321</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707028</v>
+        <v>707098</v>
       </c>
       <c r="R68" t="n">
-        <v>6635854</v>
+        <v>6635735</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8427,57 +8427,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132227423</v>
+        <v>132216648</v>
       </c>
       <c r="B69" t="n">
-        <v>96406</v>
+        <v>91913</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707098</v>
+        <v>707065</v>
       </c>
       <c r="R69" t="n">
-        <v>6635735</v>
+        <v>6635643</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8524,60 +8524,60 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132216648</v>
+        <v>132214790</v>
       </c>
       <c r="B70" t="n">
-        <v>91913</v>
+        <v>91949</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707065</v>
+        <v>707028</v>
       </c>
       <c r="R70" t="n">
-        <v>6635643</v>
+        <v>6635854</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B73" t="n">
-        <v>106222</v>
+        <v>99121</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,57 +8856,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R73" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8938,40 +8918,34 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B74" t="n">
-        <v>99121</v>
+        <v>106222</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8979,37 +8953,57 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R74" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9041,24 +9035,30 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9810,7 +9810,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -9817,42 +9817,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B82" t="n">
-        <v>57945</v>
+        <v>80647</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9860,10 +9850,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R82" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9910,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9919,6 +9909,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9929,17 +9920,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9957,32 +9953,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B83" t="n">
-        <v>80647</v>
+        <v>57945</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9990,10 +9996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R83" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10040,7 +10046,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10049,7 +10055,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10060,22 +10065,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -9817,32 +9817,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B82" t="n">
-        <v>80647</v>
+        <v>57945</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9850,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R82" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9900,7 +9910,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9909,7 +9919,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9920,22 +9929,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9953,42 +9957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B83" t="n">
-        <v>57945</v>
+        <v>80647</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9996,10 +9990,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R83" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10046,7 +10040,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10055,6 +10049,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10065,17 +10060,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7845,7 +7845,7 @@
         <v>132218114</v>
       </c>
       <c r="B63" t="n">
-        <v>84137</v>
+        <v>84139</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>132218069</v>
       </c>
       <c r="B64" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>132214935</v>
       </c>
       <c r="B65" t="n">
-        <v>92316</v>
+        <v>92322</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>132214236</v>
       </c>
       <c r="B67" t="n">
-        <v>80647</v>
+        <v>80649</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8342,45 +8342,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132227423</v>
+        <v>132216648</v>
       </c>
       <c r="B68" t="n">
-        <v>96406</v>
+        <v>91919</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707098</v>
+        <v>707065</v>
       </c>
       <c r="R68" t="n">
-        <v>6635735</v>
+        <v>6635643</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8427,57 +8427,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132216648</v>
+        <v>132227423</v>
       </c>
       <c r="B69" t="n">
-        <v>91913</v>
+        <v>96414</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707065</v>
+        <v>707098</v>
       </c>
       <c r="R69" t="n">
-        <v>6635643</v>
+        <v>6635735</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8524,12 +8524,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
         <v>132214790</v>
       </c>
       <c r="B70" t="n">
-        <v>91949</v>
+        <v>91955</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>132222629</v>
       </c>
       <c r="B71" t="n">
-        <v>106222</v>
+        <v>106230</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>132215849</v>
       </c>
       <c r="B72" t="n">
-        <v>99121</v>
+        <v>99129</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>132227426</v>
       </c>
       <c r="B73" t="n">
-        <v>99121</v>
+        <v>99129</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8945,7 +8945,7 @@
         <v>132222660</v>
       </c>
       <c r="B74" t="n">
-        <v>106222</v>
+        <v>106230</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>132227420</v>
       </c>
       <c r="B75" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9165,7 +9165,7 @@
         <v>132216402</v>
       </c>
       <c r="B76" t="n">
-        <v>107587</v>
+        <v>107595</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>132227427</v>
       </c>
       <c r="B77" t="n">
-        <v>92623</v>
+        <v>92629</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Gabriel Ekman, Martin Westberg, Viktor Lund</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9364,7 +9364,7 @@
         <v>132217832</v>
       </c>
       <c r="B78" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>132243950</v>
       </c>
       <c r="B79" t="n">
-        <v>99121</v>
+        <v>99129</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>132243953</v>
       </c>
       <c r="B80" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>132243956</v>
       </c>
       <c r="B81" t="n">
-        <v>79827</v>
+        <v>79829</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>132243945</v>
       </c>
       <c r="B82" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>132243957</v>
       </c>
       <c r="B83" t="n">
-        <v>80647</v>
+        <v>80649</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106183</v>
+        <v>106191</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>132243955</v>
       </c>
       <c r="B85" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>132243952</v>
       </c>
       <c r="B86" t="n">
-        <v>58492</v>
+        <v>58493</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B73" t="n">
-        <v>99129</v>
+        <v>106230</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,37 +8856,57 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R73" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8918,34 +8938,40 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B74" t="n">
-        <v>106230</v>
+        <v>99129</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,57 +8979,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R74" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9035,30 +9041,24 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7845,7 +7845,7 @@
         <v>132218114</v>
       </c>
       <c r="B63" t="n">
-        <v>84139</v>
+        <v>84147</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>132218069</v>
       </c>
       <c r="B64" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>132214935</v>
       </c>
       <c r="B65" t="n">
-        <v>92322</v>
+        <v>92332</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8253,7 +8253,7 @@
         <v>132214236</v>
       </c>
       <c r="B67" t="n">
-        <v>80649</v>
+        <v>80657</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>132216648</v>
       </c>
       <c r="B68" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>132227423</v>
       </c>
       <c r="B69" t="n">
-        <v>96414</v>
+        <v>96424</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
         <v>132214790</v>
       </c>
       <c r="B70" t="n">
-        <v>91955</v>
+        <v>91965</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>132222629</v>
       </c>
       <c r="B71" t="n">
-        <v>106230</v>
+        <v>106241</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>132215849</v>
       </c>
       <c r="B72" t="n">
-        <v>99129</v>
+        <v>99139</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B73" t="n">
-        <v>106230</v>
+        <v>99139</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,57 +8856,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R73" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8938,40 +8918,34 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B74" t="n">
-        <v>99129</v>
+        <v>106241</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8979,37 +8953,57 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R74" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9041,24 +9035,30 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9068,7 +9068,7 @@
         <v>132227420</v>
       </c>
       <c r="B75" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9165,7 +9165,7 @@
         <v>132216402</v>
       </c>
       <c r="B76" t="n">
-        <v>107595</v>
+        <v>107606</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9252,55 +9252,55 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132227427</v>
+        <v>132217832</v>
       </c>
       <c r="B77" t="n">
-        <v>92629</v>
+        <v>91871</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707230</v>
+        <v>707382</v>
       </c>
       <c r="R77" t="n">
-        <v>6635950</v>
+        <v>6635863</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,11 +9330,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9349,60 +9344,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gabriel Ekman, Martin Westberg, Viktor Lund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132217832</v>
+        <v>132227427</v>
       </c>
       <c r="B78" t="n">
-        <v>91861</v>
+        <v>92639</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707382</v>
+        <v>707230</v>
       </c>
       <c r="R78" t="n">
-        <v>6635863</v>
+        <v>6635950</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9432,6 +9427,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,12 +9446,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9461,7 +9461,7 @@
         <v>132243950</v>
       </c>
       <c r="B79" t="n">
-        <v>99129</v>
+        <v>99139</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9587,7 +9587,7 @@
         <v>132243953</v>
       </c>
       <c r="B80" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9708,7 +9708,7 @@
         <v>132243956</v>
       </c>
       <c r="B81" t="n">
-        <v>79829</v>
+        <v>79837</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9810,49 +9810,39 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B82" t="n">
-        <v>57946</v>
+        <v>80657</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9860,10 +9850,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R82" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9910,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9919,6 +9909,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9929,17 +9920,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9950,39 +9946,49 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B83" t="n">
-        <v>80649</v>
+        <v>57950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9990,10 +9996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R83" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10040,7 +10046,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10049,7 +10055,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10060,22 +10065,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106191</v>
+        <v>106202</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10225,7 +10225,7 @@
         <v>132243955</v>
       </c>
       <c r="B85" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10337,7 +10337,7 @@
         <v>132243952</v>
       </c>
       <c r="B86" t="n">
-        <v>58493</v>
+        <v>58497</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Martin Westberg, Cajsa Björkén, Viktor Lund, Gabriel Ekman, Joakim Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -9461,7 +9461,7 @@
         <v>132243950</v>
       </c>
       <c r="B79" t="n">
-        <v>99139</v>
+        <v>99140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9817,32 +9817,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B82" t="n">
-        <v>80657</v>
+        <v>57950</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9850,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R82" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9900,7 +9910,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9909,7 +9919,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9920,22 +9929,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9953,42 +9957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B83" t="n">
-        <v>57950</v>
+        <v>80657</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9996,10 +9990,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R83" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10046,7 +10040,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10055,6 +10049,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10065,17 +10060,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106202</v>
+        <v>106203</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7942,7 +7942,7 @@
         <v>132218069</v>
       </c>
       <c r="B64" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>132214935</v>
       </c>
       <c r="B65" t="n">
-        <v>92332</v>
+        <v>92333</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8342,45 +8342,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132216648</v>
+        <v>132227423</v>
       </c>
       <c r="B68" t="n">
-        <v>91929</v>
+        <v>96426</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707065</v>
+        <v>707098</v>
       </c>
       <c r="R68" t="n">
-        <v>6635643</v>
+        <v>6635735</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8427,57 +8427,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132227423</v>
+        <v>132216648</v>
       </c>
       <c r="B69" t="n">
-        <v>96424</v>
+        <v>91930</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707098</v>
+        <v>707065</v>
       </c>
       <c r="R69" t="n">
-        <v>6635735</v>
+        <v>6635643</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8524,12 +8524,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
         <v>132214790</v>
       </c>
       <c r="B70" t="n">
-        <v>91965</v>
+        <v>91966</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>132222629</v>
       </c>
       <c r="B71" t="n">
-        <v>106241</v>
+        <v>106243</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>132215849</v>
       </c>
       <c r="B72" t="n">
-        <v>99139</v>
+        <v>99141</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>132227426</v>
       </c>
       <c r="B73" t="n">
-        <v>99139</v>
+        <v>99141</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>132222660</v>
       </c>
       <c r="B74" t="n">
-        <v>106241</v>
+        <v>106243</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>132216402</v>
       </c>
       <c r="B76" t="n">
-        <v>107606</v>
+        <v>107608</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9252,55 +9252,55 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132217832</v>
+        <v>132227427</v>
       </c>
       <c r="B77" t="n">
-        <v>91871</v>
+        <v>92640</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707382</v>
+        <v>707230</v>
       </c>
       <c r="R77" t="n">
-        <v>6635863</v>
+        <v>6635950</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,6 +9330,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9344,60 +9349,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132227427</v>
+        <v>132217832</v>
       </c>
       <c r="B78" t="n">
-        <v>92639</v>
+        <v>91872</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707230</v>
+        <v>707382</v>
       </c>
       <c r="R78" t="n">
-        <v>6635950</v>
+        <v>6635863</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,11 +9432,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,12 +9446,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9461,7 +9461,7 @@
         <v>132243950</v>
       </c>
       <c r="B79" t="n">
-        <v>99140</v>
+        <v>99141</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106203</v>
+        <v>106204</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8342,45 +8342,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132227423</v>
+        <v>132216648</v>
       </c>
       <c r="B68" t="n">
-        <v>96426</v>
+        <v>91930</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707098</v>
+        <v>707065</v>
       </c>
       <c r="R68" t="n">
-        <v>6635735</v>
+        <v>6635643</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8427,60 +8427,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132216648</v>
+        <v>132214790</v>
       </c>
       <c r="B69" t="n">
-        <v>91930</v>
+        <v>91966</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707065</v>
+        <v>707028</v>
       </c>
       <c r="R69" t="n">
-        <v>6635643</v>
+        <v>6635854</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132214790</v>
+        <v>132227423</v>
       </c>
       <c r="B70" t="n">
-        <v>91966</v>
+        <v>96426</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8547,37 +8547,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>2671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707028</v>
+        <v>707098</v>
       </c>
       <c r="R70" t="n">
-        <v>6635854</v>
+        <v>6635735</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8621,12 +8621,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8636,7 +8636,7 @@
         <v>132222629</v>
       </c>
       <c r="B71" t="n">
-        <v>106243</v>
+        <v>106244</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B73" t="n">
-        <v>99141</v>
+        <v>106244</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,37 +8856,57 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R73" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8918,34 +8938,40 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B74" t="n">
-        <v>106243</v>
+        <v>99141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,57 +8979,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R74" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9035,30 +9041,24 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9165,7 +9165,7 @@
         <v>132216402</v>
       </c>
       <c r="B76" t="n">
-        <v>107608</v>
+        <v>107609</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9259,48 +9259,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132227427</v>
+        <v>132217832</v>
       </c>
       <c r="B77" t="n">
-        <v>92640</v>
+        <v>91872</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707230</v>
+        <v>707382</v>
       </c>
       <c r="R77" t="n">
-        <v>6635950</v>
+        <v>6635863</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,11 +9330,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9349,60 +9344,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132217832</v>
+        <v>132227427</v>
       </c>
       <c r="B78" t="n">
-        <v>91872</v>
+        <v>92640</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707382</v>
+        <v>707230</v>
       </c>
       <c r="R78" t="n">
-        <v>6635863</v>
+        <v>6635950</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9432,6 +9427,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,12 +9446,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9817,42 +9817,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B82" t="n">
-        <v>57950</v>
+        <v>80657</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9860,10 +9850,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R82" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9910,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9919,6 +9909,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9929,17 +9920,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9957,32 +9953,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B83" t="n">
-        <v>80657</v>
+        <v>57950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9990,10 +9996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R83" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10040,7 +10046,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10049,7 +10055,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10060,22 +10065,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106204</v>
+        <v>106205</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7845,7 +7845,7 @@
         <v>132218114</v>
       </c>
       <c r="B63" t="n">
-        <v>84147</v>
+        <v>84148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>132218069</v>
       </c>
       <c r="B64" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>132214935</v>
       </c>
       <c r="B65" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>132214236</v>
       </c>
       <c r="B67" t="n">
-        <v>80657</v>
+        <v>80658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>132216648</v>
       </c>
       <c r="B68" t="n">
-        <v>91930</v>
+        <v>91931</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132214790</v>
+        <v>132227423</v>
       </c>
       <c r="B69" t="n">
-        <v>91966</v>
+        <v>96427</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8450,37 +8450,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707028</v>
+        <v>707098</v>
       </c>
       <c r="R69" t="n">
-        <v>6635854</v>
+        <v>6635735</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8524,22 +8524,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132227423</v>
+        <v>132214790</v>
       </c>
       <c r="B70" t="n">
-        <v>96426</v>
+        <v>91967</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8547,37 +8547,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2671</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707098</v>
+        <v>707028</v>
       </c>
       <c r="R70" t="n">
-        <v>6635735</v>
+        <v>6635854</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8621,12 +8621,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8636,7 +8636,7 @@
         <v>132222629</v>
       </c>
       <c r="B71" t="n">
-        <v>106244</v>
+        <v>106245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>132215849</v>
       </c>
       <c r="B72" t="n">
-        <v>99141</v>
+        <v>99142</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B73" t="n">
-        <v>106244</v>
+        <v>99142</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,57 +8856,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R73" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8938,40 +8918,34 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B74" t="n">
-        <v>99141</v>
+        <v>106245</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8979,37 +8953,57 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R74" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9041,24 +9035,30 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9068,7 +9068,7 @@
         <v>132227420</v>
       </c>
       <c r="B75" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>132216402</v>
       </c>
       <c r="B76" t="n">
-        <v>107609</v>
+        <v>107610</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>132217832</v>
       </c>
       <c r="B77" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>132227427</v>
       </c>
       <c r="B78" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>132243950</v>
       </c>
       <c r="B79" t="n">
-        <v>99141</v>
+        <v>99142</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>132243953</v>
       </c>
       <c r="B80" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>132243956</v>
       </c>
       <c r="B81" t="n">
-        <v>79837</v>
+        <v>79838</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9817,32 +9817,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B82" t="n">
-        <v>80657</v>
+        <v>57951</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9850,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R82" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9900,7 +9910,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9909,7 +9919,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9920,22 +9929,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9953,42 +9957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B83" t="n">
-        <v>57950</v>
+        <v>80658</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9996,10 +9990,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R83" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10046,7 +10040,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10055,6 +10049,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10065,17 +10060,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106205</v>
+        <v>106206</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>132243955</v>
       </c>
       <c r="B85" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>132243952</v>
       </c>
       <c r="B86" t="n">
-        <v>58497</v>
+        <v>58498</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7845,7 +7845,7 @@
         <v>132218114</v>
       </c>
       <c r="B63" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>132218069</v>
       </c>
       <c r="B64" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>132214935</v>
       </c>
       <c r="B65" t="n">
-        <v>92334</v>
+        <v>92336</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>132216648</v>
       </c>
       <c r="B68" t="n">
-        <v>91931</v>
+        <v>91933</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132227423</v>
+        <v>132214790</v>
       </c>
       <c r="B69" t="n">
-        <v>96427</v>
+        <v>91969</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8450,37 +8450,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707098</v>
+        <v>707028</v>
       </c>
       <c r="R69" t="n">
-        <v>6635735</v>
+        <v>6635854</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8524,22 +8524,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132214790</v>
+        <v>132227423</v>
       </c>
       <c r="B70" t="n">
-        <v>91967</v>
+        <v>96429</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8547,37 +8547,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>2671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707028</v>
+        <v>707098</v>
       </c>
       <c r="R70" t="n">
-        <v>6635854</v>
+        <v>6635735</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8621,12 +8621,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8636,7 +8636,7 @@
         <v>132222629</v>
       </c>
       <c r="B71" t="n">
-        <v>106245</v>
+        <v>106247</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>132215849</v>
       </c>
       <c r="B72" t="n">
-        <v>99142</v>
+        <v>99144</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>132227426</v>
       </c>
       <c r="B73" t="n">
-        <v>99142</v>
+        <v>99144</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8945,7 +8945,7 @@
         <v>132222660</v>
       </c>
       <c r="B74" t="n">
-        <v>106245</v>
+        <v>106247</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9165,7 +9165,7 @@
         <v>132216402</v>
       </c>
       <c r="B76" t="n">
-        <v>107610</v>
+        <v>107612</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9259,48 +9259,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132217832</v>
+        <v>132227427</v>
       </c>
       <c r="B77" t="n">
-        <v>91873</v>
+        <v>92643</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707382</v>
+        <v>707230</v>
       </c>
       <c r="R77" t="n">
-        <v>6635863</v>
+        <v>6635950</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,6 +9330,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9344,60 +9349,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132227427</v>
+        <v>132217832</v>
       </c>
       <c r="B78" t="n">
-        <v>92641</v>
+        <v>91875</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707230</v>
+        <v>707382</v>
       </c>
       <c r="R78" t="n">
-        <v>6635950</v>
+        <v>6635863</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,11 +9432,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,12 +9446,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9461,7 +9461,7 @@
         <v>132243950</v>
       </c>
       <c r="B79" t="n">
-        <v>99142</v>
+        <v>99144</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9817,42 +9817,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B82" t="n">
-        <v>57951</v>
+        <v>80658</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9860,10 +9850,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R82" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9910,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9919,6 +9909,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9929,17 +9920,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9957,32 +9953,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B83" t="n">
-        <v>80658</v>
+        <v>57951</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9990,10 +9996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R83" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10040,7 +10046,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10049,7 +10055,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10060,22 +10065,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106206</v>
+        <v>106208</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7845,7 +7845,7 @@
         <v>132218114</v>
       </c>
       <c r="B63" t="n">
-        <v>84150</v>
+        <v>84151</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>132218069</v>
       </c>
       <c r="B64" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>132214935</v>
       </c>
       <c r="B65" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>132214236</v>
       </c>
       <c r="B67" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8342,45 +8342,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132216648</v>
+        <v>132227423</v>
       </c>
       <c r="B68" t="n">
-        <v>91933</v>
+        <v>96430</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707065</v>
+        <v>707098</v>
       </c>
       <c r="R68" t="n">
-        <v>6635643</v>
+        <v>6635735</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8427,60 +8427,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132214790</v>
+        <v>132216648</v>
       </c>
       <c r="B69" t="n">
-        <v>91969</v>
+        <v>91934</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707028</v>
+        <v>707065</v>
       </c>
       <c r="R69" t="n">
-        <v>6635854</v>
+        <v>6635643</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132227423</v>
+        <v>132214790</v>
       </c>
       <c r="B70" t="n">
-        <v>96429</v>
+        <v>91970</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8547,37 +8547,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2671</v>
+        <v>5321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707098</v>
+        <v>707028</v>
       </c>
       <c r="R70" t="n">
-        <v>6635735</v>
+        <v>6635854</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8621,12 +8621,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman, Joakim Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8636,7 +8636,7 @@
         <v>132222629</v>
       </c>
       <c r="B71" t="n">
-        <v>106247</v>
+        <v>106248</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>132215849</v>
       </c>
       <c r="B72" t="n">
-        <v>99144</v>
+        <v>99145</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B73" t="n">
-        <v>99144</v>
+        <v>106248</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,37 +8856,57 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R73" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8918,34 +8938,40 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman, Joakim Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B74" t="n">
-        <v>106247</v>
+        <v>99145</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,57 +8979,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R74" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9035,30 +9041,24 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -9068,7 +9068,7 @@
         <v>132227420</v>
       </c>
       <c r="B75" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gabriel Ekman, Joakim Ekman, Martin Westberg, Viktor Lund</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9165,7 +9165,7 @@
         <v>132216402</v>
       </c>
       <c r="B76" t="n">
-        <v>107612</v>
+        <v>107613</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>132227427</v>
       </c>
       <c r="B77" t="n">
-        <v>92643</v>
+        <v>92644</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>132217832</v>
       </c>
       <c r="B78" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>132243950</v>
       </c>
       <c r="B79" t="n">
-        <v>99144</v>
+        <v>99145</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         <v>132243956</v>
       </c>
       <c r="B81" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9817,32 +9817,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B82" t="n">
-        <v>80658</v>
+        <v>57951</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9850,10 +9860,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R82" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9900,7 +9910,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9909,7 +9919,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9920,22 +9929,17 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9953,42 +9957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B83" t="n">
-        <v>57951</v>
+        <v>80659</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9996,10 +9990,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R83" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10046,7 +10040,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10055,6 +10049,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10065,17 +10060,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10096,7 +10096,7 @@
         <v>132243949</v>
       </c>
       <c r="B84" t="n">
-        <v>106208</v>
+        <v>106209</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>132243955</v>
       </c>
       <c r="B85" t="n">
-        <v>80393</v>
+        <v>80394</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8845,10 +8845,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132222660</v>
+        <v>132227426</v>
       </c>
       <c r="B73" t="n">
-        <v>106248</v>
+        <v>99145</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8856,57 +8856,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707127</v>
+        <v>707352</v>
       </c>
       <c r="R73" t="n">
-        <v>6635639</v>
+        <v>6635802</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8938,40 +8918,34 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>C:a 10 ex.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132227426</v>
+        <v>132222660</v>
       </c>
       <c r="B74" t="n">
-        <v>99145</v>
+        <v>106248</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8979,37 +8953,57 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219862</v>
+        <v>221144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707352</v>
+        <v>707127</v>
       </c>
       <c r="R74" t="n">
-        <v>6635802</v>
+        <v>6635639</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9041,24 +9035,30 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8342,45 +8342,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132227423</v>
+        <v>132216648</v>
       </c>
       <c r="B68" t="n">
-        <v>96430</v>
+        <v>91934</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707098</v>
+        <v>707065</v>
       </c>
       <c r="R68" t="n">
-        <v>6635735</v>
+        <v>6635643</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8427,57 +8427,57 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132216648</v>
+        <v>132227423</v>
       </c>
       <c r="B69" t="n">
-        <v>91934</v>
+        <v>96430</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707065</v>
+        <v>707098</v>
       </c>
       <c r="R69" t="n">
-        <v>6635643</v>
+        <v>6635735</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8524,12 +8524,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9259,48 +9259,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132227427</v>
+        <v>132217832</v>
       </c>
       <c r="B77" t="n">
-        <v>92644</v>
+        <v>91876</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707230</v>
+        <v>707382</v>
       </c>
       <c r="R77" t="n">
-        <v>6635950</v>
+        <v>6635863</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,11 +9330,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9349,60 +9344,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132217832</v>
+        <v>132227427</v>
       </c>
       <c r="B78" t="n">
-        <v>91876</v>
+        <v>92644</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707382</v>
+        <v>707230</v>
       </c>
       <c r="R78" t="n">
-        <v>6635863</v>
+        <v>6635950</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9432,6 +9427,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,12 +9446,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -7932,7 +7932,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8342,48 +8342,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132216648</v>
+        <v>132214790</v>
       </c>
       <c r="B68" t="n">
-        <v>91934</v>
+        <v>91970</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707065</v>
+        <v>707028</v>
       </c>
       <c r="R68" t="n">
-        <v>6635643</v>
+        <v>6635854</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8439,45 +8439,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132227423</v>
+        <v>132216648</v>
       </c>
       <c r="B69" t="n">
-        <v>96430</v>
+        <v>91934</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707098</v>
+        <v>707065</v>
       </c>
       <c r="R69" t="n">
-        <v>6635735</v>
+        <v>6635643</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8524,22 +8524,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132214790</v>
+        <v>132227423</v>
       </c>
       <c r="B70" t="n">
-        <v>91970</v>
+        <v>96430</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8547,37 +8547,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5321</v>
+        <v>2671</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707028</v>
+        <v>707098</v>
       </c>
       <c r="R70" t="n">
-        <v>6635854</v>
+        <v>6635735</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8621,12 +8621,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9259,48 +9259,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132217832</v>
+        <v>132227427</v>
       </c>
       <c r="B77" t="n">
-        <v>91876</v>
+        <v>92644</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707382</v>
+        <v>707230</v>
       </c>
       <c r="R77" t="n">
-        <v>6635863</v>
+        <v>6635950</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,6 +9330,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9344,60 +9349,60 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132227427</v>
+        <v>132217832</v>
       </c>
       <c r="B78" t="n">
-        <v>92644</v>
+        <v>91876</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>757</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707230</v>
+        <v>707382</v>
       </c>
       <c r="R78" t="n">
-        <v>6635950</v>
+        <v>6635863</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9427,11 +9432,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9446,12 +9446,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
+          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9817,42 +9817,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132243945</v>
+        <v>132243957</v>
       </c>
       <c r="B82" t="n">
-        <v>57951</v>
+        <v>80659</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9860,10 +9850,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>707094</v>
+        <v>706941</v>
       </c>
       <c r="R82" t="n">
-        <v>6635643</v>
+        <v>6635897</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9910,7 +9900,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>På en klen aspgren på en stor asplåga.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9919,6 +9909,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9929,17 +9920,22 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Dead branch  # Populus tremula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9957,32 +9953,42 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243957</v>
+        <v>132243945</v>
       </c>
       <c r="B83" t="n">
-        <v>80659</v>
+        <v>57951</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228430</v>
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9990,10 +9996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>706941</v>
+        <v>707094</v>
       </c>
       <c r="R83" t="n">
-        <v>6635897</v>
+        <v>6635643</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10040,7 +10046,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10049,7 +10055,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10060,22 +10065,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Död gren</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Dead branch  # Populus tremula</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -8342,10 +8342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132214790</v>
+        <v>132227423</v>
       </c>
       <c r="B68" t="n">
-        <v>91970</v>
+        <v>96430</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5321</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707028</v>
+        <v>707098</v>
       </c>
       <c r="R68" t="n">
-        <v>6635854</v>
+        <v>6635735</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8427,60 +8427,60 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132216648</v>
+        <v>132214790</v>
       </c>
       <c r="B69" t="n">
-        <v>91934</v>
+        <v>91970</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707065</v>
+        <v>707028</v>
       </c>
       <c r="R69" t="n">
-        <v>6635643</v>
+        <v>6635854</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8536,45 +8536,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132227423</v>
+        <v>132216648</v>
       </c>
       <c r="B70" t="n">
-        <v>96430</v>
+        <v>91934</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2671</v>
+        <v>5442</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707098</v>
+        <v>707065</v>
       </c>
       <c r="R70" t="n">
-        <v>6635735</v>
+        <v>6635643</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8621,12 +8621,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73253922</v>
+        <v>82169679</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borg, 600 m WNW, Estuna, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707123.7009958185</v>
+        <v>707181</v>
       </c>
       <c r="R2" t="n">
-        <v>6635743.081038792</v>
+        <v>6636034</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På liggande asplåga S stigen och Ö om ostbranten. Nedre delen av sluttning. Äldre asprik, grandominerad barrskog. Medobservatör Edvin Stighäll.</t>
+          <t>På gammal rötskadad tallåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73253929</v>
+        <v>82169838</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,47 +793,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borg, 400 m WNW, Estuna, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>707314.3590831459</v>
+        <v>707322</v>
       </c>
       <c r="R3" t="n">
-        <v>6635656.923176032</v>
+        <v>6635990</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,27 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>S stigen. Mossrik äldre barrskog. Medobs Edvin Stighäll.</t>
+          <t>På högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,75 +876,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73253943</v>
+        <v>113024359</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>340</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Borg, 450 m NW, Estuna, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>707356.2835180851</v>
+        <v>707087</v>
       </c>
       <c r="R4" t="n">
-        <v>6635810.51341826</v>
+        <v>6635689</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,27 +953,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mossig äldre barrskog. Medobs Edvin Stighäll.</t>
+          <t>minst 9 plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,81 +972,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82169826</v>
+        <v>113409392</v>
       </c>
       <c r="B5" t="n">
-        <v>5402</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101377</v>
+        <v>340</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Östra Eka, SO om (*ryl* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>707322.0136748437</v>
+        <v>707086</v>
       </c>
       <c r="R5" t="n">
-        <v>6635990.089915751</v>
+        <v>6635689</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,29 +1062,24 @@
           <t>Estuna</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>AB-Nor-1850</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnagspår på högstubbe av asp.</t>
+          <t>Östra Eka, SO om, Obskoord: 6635468/1662019/15 m (). minst 9 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,61 +1088,72 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82257673</v>
+        <v>132243949</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>340</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ryl</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chimaphila umbellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1229,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>707522.0265398819</v>
+        <v>707078</v>
       </c>
       <c r="R6" t="n">
-        <v>6635935.22441985</v>
+        <v>6635703</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1259,27 +1191,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,71 +1219,68 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Blockig, gles blandskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>82257697</v>
+        <v>132227427</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>757</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>707468.1729395655</v>
+        <v>707230</v>
       </c>
       <c r="R7" t="n">
-        <v>6635877.766898692</v>
+        <v>6635950</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1380,27 +1304,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,81 +1323,66 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82169550</v>
+        <v>113024356</v>
       </c>
       <c r="B8" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>937</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>707170.0082304243</v>
+        <v>707016</v>
       </c>
       <c r="R8" t="n">
-        <v>6635990.173671377</v>
+        <v>6635832</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1507,22 +1406,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på granlåga. kollekt taget</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,75 +1425,70 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>82257772</v>
+        <v>132216534</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1026</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östra Eka, SSO om, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>706973.1330367273</v>
+        <v>707041</v>
       </c>
       <c r="R9" t="n">
-        <v>6635816.860231626</v>
+        <v>6635647</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1623,27 +1512,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,78 +1526,63 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>82169013</v>
+        <v>132243956</v>
       </c>
       <c r="B10" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>1026</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ädellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Megalaria grossa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Pers. ex Nyl.) Hafellner</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>707089.9431061175</v>
+        <v>707009</v>
       </c>
       <c r="R10" t="n">
-        <v>6635940.83881683</v>
+        <v>6635864</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1750,22 +1609,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,34 +1633,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>82257709</v>
+        <v>131431280</v>
       </c>
       <c r="B11" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,40 +1667,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1114</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelekslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lecanographa amylacea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Haggård, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>707453.0720645101</v>
+        <v>707019</v>
       </c>
       <c r="R11" t="n">
-        <v>6635867.848353209</v>
+        <v>6635839</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,22 +1721,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,34 +1735,32 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>82169643</v>
+        <v>82257772</v>
       </c>
       <c r="B12" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,42 +1768,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Östra Eka, SSO om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>707160.7770376395</v>
+        <v>706973</v>
       </c>
       <c r="R12" t="n">
-        <v>6636001.757486283</v>
+        <v>6635817</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1990,19 +1828,14 @@
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,6 +1844,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2029,15 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>82169956</v>
+        <v>73253922</v>
       </c>
       <c r="B13" t="n">
-        <v>89780</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,40 +1874,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Borg, 600 m WNW, Estuna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>707408.7955342702</v>
+        <v>707124</v>
       </c>
       <c r="R13" t="n">
-        <v>6636127.017173918</v>
+        <v>6635743</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2102,34 +1938,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På barklös tallåga. Fruktkroppen kan eventuellt vara den mer ovanliga och rödlistade laxgröppan.</t>
+          <t>På liggande asplåga S stigen och Ö om ostbranten. Nedre delen av sluttning. Äldre asprik, grandominerad barrskog. Medobservatör Edvin Stighäll.</t>
         </is>
       </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
@@ -2138,27 +1964,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>82169734</v>
+        <v>82257888</v>
       </c>
       <c r="B14" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,43 +1987,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102306</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Östra Eka, SSO om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>707226.1213122472</v>
+        <v>707173</v>
       </c>
       <c r="R14" t="n">
-        <v>6635934.826649489</v>
+        <v>6635664</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2232,19 +2055,14 @@
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 fruktkropp på högstubbe av asp och 2 fruktkroppar på  tillhörande låga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2272,15 +2090,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>82169803</v>
+        <v>82258548</v>
       </c>
       <c r="B15" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2288,37 +2101,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Östra Eka, SSO om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>707351.193159097</v>
+        <v>707163</v>
       </c>
       <c r="R15" t="n">
-        <v>6635946.852010466</v>
+        <v>6635679</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2348,19 +2169,14 @@
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2388,41 +2204,44 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>82257764</v>
+        <v>82258553</v>
       </c>
       <c r="B16" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2431,10 +2250,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>706942.8934941392</v>
+        <v>707109</v>
       </c>
       <c r="R16" t="n">
-        <v>6635870.125813372</v>
+        <v>6635755</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2464,24 +2283,14 @@
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På låga och högstubbe av gran.</t>
+          <t>På asplåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2509,15 +2318,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>82170031</v>
+        <v>112801374</v>
       </c>
       <c r="B17" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,41 +2329,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>707493.8359126796</v>
+        <v>707244</v>
       </c>
       <c r="R17" t="n">
-        <v>6636267.877684197</v>
+        <v>6635642</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2583,27 +2384,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal asp.</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2612,34 +2408,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>82169978</v>
+        <v>132218114</v>
       </c>
       <c r="B18" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84198</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2647,41 +2437,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>1444</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707433.1468278889</v>
+        <v>707052</v>
       </c>
       <c r="R18" t="n">
-        <v>6636161.145014999</v>
+        <v>6635913</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2705,22 +2491,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,81 +2505,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>82169778</v>
+        <v>112801254</v>
       </c>
       <c r="B19" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>1988</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707269.027942433</v>
+        <v>707295</v>
       </c>
       <c r="R19" t="n">
-        <v>6635917.056654949</v>
+        <v>6635639</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2827,22 +2589,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2851,83 +2613,66 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>82258553</v>
+        <v>113024358</v>
       </c>
       <c r="B20" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1205</v>
+        <v>1988</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östra Eka, SSO om, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707108.9034295762</v>
+        <v>707081</v>
       </c>
       <c r="R20" t="n">
-        <v>6635754.859406611</v>
+        <v>6635696</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2951,27 +2696,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På asplåga.</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2980,83 +2710,71 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>82257888</v>
+        <v>112798700</v>
       </c>
       <c r="B21" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>2058</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östra Eka, SSO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707173.0516201046</v>
+        <v>707292</v>
       </c>
       <c r="R21" t="n">
-        <v>6635664.160194444</v>
+        <v>6635701</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3080,27 +2798,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>1 fruktkropp på högstubbe av asp och 2 fruktkroppar på  tillhörande låga.</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3109,34 +2822,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>82258548</v>
+        <v>82169978</v>
       </c>
       <c r="B22" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3144,45 +2851,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1205</v>
+        <v>2180</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östra Eka, SSO om, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707163.1199063803</v>
+        <v>707433</v>
       </c>
       <c r="R22" t="n">
-        <v>6635679.235195231</v>
+        <v>6636161</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3212,24 +2912,9 @@
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3257,15 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>82169409</v>
+        <v>132227423</v>
       </c>
       <c r="B23" t="n">
-        <v>4808</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,46 +2953,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101675</v>
+        <v>2671</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707122.8071197285</v>
+        <v>707098</v>
       </c>
       <c r="R23" t="n">
-        <v>6635931.077303519</v>
+        <v>6635735</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3336,27 +3007,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gnagspår på högstubbe av asp.</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3365,34 +3021,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>82169875</v>
+        <v>112801334</v>
       </c>
       <c r="B24" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3400,40 +3050,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707315.218439994</v>
+        <v>707295</v>
       </c>
       <c r="R24" t="n">
-        <v>6635985.173252858</v>
+        <v>6635639</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3457,27 +3105,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På torrgran.</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3486,34 +3129,28 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>82169853</v>
+        <v>112801408</v>
       </c>
       <c r="B25" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3521,40 +3158,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6439</v>
+        <v>3215</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707322.0136748437</v>
+        <v>707224</v>
       </c>
       <c r="R25" t="n">
-        <v>6635990.089915751</v>
+        <v>6635624</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3578,27 +3213,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På högstubbe av asp.</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3607,34 +3237,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>82170167</v>
+        <v>112800970</v>
       </c>
       <c r="B26" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3642,40 +3266,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>3884</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707526.8152853849</v>
+        <v>707362</v>
       </c>
       <c r="R26" t="n">
-        <v>6636021.194787313</v>
+        <v>6635699</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3699,22 +3321,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3723,56 +3345,50 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>82257769</v>
+        <v>82169956</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>4217</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3781,14 +3397,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Östra Eka, SSO om, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706957.9973611896</v>
+        <v>707409</v>
       </c>
       <c r="R27" t="n">
-        <v>6635861.893328619</v>
+        <v>6636127</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3818,31 +3434,21 @@
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2020-02-12</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran.</t>
+          <t>På barklös tallåga. Fruktkroppen kan eventuellt vara den mer ovanliga och rödlistade laxgröppan.</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
@@ -3863,15 +3469,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>82169838</v>
+        <v>132214935</v>
       </c>
       <c r="B28" t="n">
-        <v>73680</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3879,40 +3480,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>306</v>
+        <v>4217</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707322.0136748437</v>
+        <v>707044</v>
       </c>
       <c r="R28" t="n">
-        <v>6635990.089915751</v>
+        <v>6635846</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3936,27 +3534,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På högstubbe av asp.</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3965,34 +3548,43 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>82169931</v>
+        <v>112800547</v>
       </c>
       <c r="B29" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4000,40 +3592,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707383.1758869773</v>
+        <v>707340</v>
       </c>
       <c r="R29" t="n">
-        <v>6636007.117783794</v>
+        <v>6635819</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4057,27 +3647,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal tallstubbe.</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4086,81 +3671,67 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>82169771</v>
+        <v>112801723</v>
       </c>
       <c r="B30" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707269.027942433</v>
+        <v>707171</v>
       </c>
       <c r="R30" t="n">
-        <v>6635917.056654949</v>
+        <v>6635473</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4184,22 +3755,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4208,81 +3779,76 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>82169652</v>
+        <v>73253943</v>
       </c>
       <c r="B31" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100526</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Borg, 450 m NW, Estuna, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707160.7770376395</v>
+        <v>707356</v>
       </c>
       <c r="R31" t="n">
-        <v>6636001.757486283</v>
+        <v>6635811</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4306,27 +3872,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gnagspår på torrgran.</t>
+          <t>Mossig äldre barrskog. Medobs Edvin Stighäll.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4342,69 +3898,61 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>82169679</v>
+        <v>112801234</v>
       </c>
       <c r="B32" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>4405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707181.1882496479</v>
+        <v>707301</v>
       </c>
       <c r="R32" t="n">
-        <v>6636034.152179915</v>
+        <v>6635643</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4428,27 +3976,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gammal rötskadad tallåga.</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4457,34 +4000,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>82170052</v>
+        <v>112801348</v>
       </c>
       <c r="B33" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4492,41 +4029,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>4405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707512.8449867895</v>
+        <v>707295</v>
       </c>
       <c r="R33" t="n">
-        <v>6636298.177716144</v>
+        <v>6635639</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4550,22 +4084,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4574,34 +4108,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>82169571</v>
+        <v>112801220</v>
       </c>
       <c r="B34" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4609,46 +4137,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102306</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707199.1237438589</v>
+        <v>707301</v>
       </c>
       <c r="R34" t="n">
-        <v>6635984.236803809</v>
+        <v>6635640</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4672,22 +4192,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4696,34 +4216,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112801374</v>
+        <v>112801302</v>
       </c>
       <c r="B35" t="n">
-        <v>90551</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4731,35 +4245,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1339</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707245</v>
+        <v>707295</v>
       </c>
       <c r="R35" t="n">
-        <v>6635642</v>
+        <v>6635639</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4791,7 +4305,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4801,7 +4315,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4828,15 +4342,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112801334</v>
+        <v>131431278</v>
       </c>
       <c r="B36" t="n">
-        <v>89714</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4844,35 +4353,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>5321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Haggård, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707295</v>
+        <v>707150</v>
       </c>
       <c r="R36" t="n">
-        <v>6635639</v>
+        <v>6636054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4899,22 +4407,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4923,33 +4421,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112801254</v>
+        <v>132214790</v>
       </c>
       <c r="B37" t="n">
-        <v>85772</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92031</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4957,38 +4455,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1988</v>
+        <v>5321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707295</v>
+        <v>707028</v>
       </c>
       <c r="R37" t="n">
-        <v>6635639</v>
+        <v>6635854</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5012,22 +4509,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5047,61 +4534,58 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112801408</v>
+        <v>82257709</v>
       </c>
       <c r="B38" t="n">
-        <v>89714</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3215</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707224</v>
+        <v>707453</v>
       </c>
       <c r="R38" t="n">
-        <v>6635624</v>
+        <v>6635868</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5125,22 +4609,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5149,69 +4623,64 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112798925</v>
+        <v>132216648</v>
       </c>
       <c r="B39" t="n">
-        <v>91220</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91995</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>5442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707356</v>
+        <v>707065</v>
       </c>
       <c r="R39" t="n">
-        <v>6635722</v>
+        <v>6635643</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5238,22 +4707,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5273,61 +4732,58 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112800547</v>
+        <v>82169875</v>
       </c>
       <c r="B40" t="n">
-        <v>91191</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707340</v>
+        <v>707315</v>
       </c>
       <c r="R40" t="n">
-        <v>6635819</v>
+        <v>6635985</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5351,22 +4807,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5375,33 +4826,29 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112801348</v>
+        <v>82257697</v>
       </c>
       <c r="B41" t="n">
-        <v>86741</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5409,38 +4856,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4405</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707295</v>
+        <v>707468</v>
       </c>
       <c r="R41" t="n">
-        <v>6635639</v>
+        <v>6635878</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5464,22 +4913,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5488,33 +4932,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112800985</v>
+        <v>132217832</v>
       </c>
       <c r="B42" t="n">
-        <v>91220</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5522,38 +4962,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707359</v>
+        <v>707382</v>
       </c>
       <c r="R42" t="n">
-        <v>6635714</v>
+        <v>6635863</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5577,22 +5016,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:59</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5612,58 +5041,55 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112801220</v>
+        <v>112813338</v>
       </c>
       <c r="B43" t="n">
-        <v>90865</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707301</v>
+        <v>707218</v>
       </c>
       <c r="R43" t="n">
-        <v>6635640</v>
+        <v>6635565</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5695,7 +5121,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5705,7 +5131,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Luktar starkt "skoaffär". Växte intill grov gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5714,6 +5145,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5732,19 +5164,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112801385</v>
+        <v>73253929</v>
       </c>
       <c r="B44" t="n">
-        <v>91220</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5757,29 +5184,38 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Borg, 400 m WNW, Estuna, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707245</v>
+        <v>707314</v>
       </c>
       <c r="R44" t="n">
-        <v>6635642</v>
+        <v>6635657</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5803,22 +5239,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2018-09-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>S stigen. Mossrik äldre barrskog. Medobs Edvin Stighäll.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5827,72 +5258,70 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112801302</v>
+        <v>82169803</v>
       </c>
       <c r="B45" t="n">
-        <v>90865</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707295</v>
+        <v>707351</v>
       </c>
       <c r="R45" t="n">
-        <v>6635639</v>
+        <v>6635947</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5916,22 +5345,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5940,33 +5359,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112801723</v>
+        <v>112798925</v>
       </c>
       <c r="B46" t="n">
-        <v>91191</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5974,35 +5389,35 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707171</v>
+        <v>707356</v>
       </c>
       <c r="R46" t="n">
-        <v>6635473</v>
+        <v>6635721</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6034,7 +5449,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6044,7 +5459,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6071,15 +5486,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112798570</v>
+        <v>112800935</v>
       </c>
       <c r="B47" t="n">
-        <v>89956</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6087,37 +5497,35 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707251</v>
+        <v>707362</v>
       </c>
       <c r="R47" t="n">
-        <v>6635687</v>
+        <v>6635739</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6149,7 +5557,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6159,12 +5567,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gren på stående död gran.</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6173,7 +5576,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6192,51 +5594,46 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112798700</v>
+        <v>112800985</v>
       </c>
       <c r="B48" t="n">
-        <v>91207</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2058</v>
+        <v>5964</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707292</v>
+        <v>707359</v>
       </c>
       <c r="R48" t="n">
-        <v>6635701</v>
+        <v>6635714</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6268,7 +5665,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6278,7 +5675,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6305,51 +5702,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112801234</v>
+        <v>112801385</v>
       </c>
       <c r="B49" t="n">
-        <v>86741</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4405</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707301</v>
+        <v>707244</v>
       </c>
       <c r="R49" t="n">
-        <v>6635643</v>
+        <v>6635642</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6381,7 +5773,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6391,7 +5783,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6418,51 +5810,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112800970</v>
+        <v>112801678</v>
       </c>
       <c r="B50" t="n">
-        <v>90486</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3884</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707362</v>
+        <v>707208</v>
       </c>
       <c r="R50" t="n">
-        <v>6635699</v>
+        <v>6635529</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6494,7 +5881,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6504,7 +5891,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6531,19 +5918,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112800935</v>
+        <v>113024361</v>
       </c>
       <c r="B51" t="n">
-        <v>91220</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -6556,29 +5938,28 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707363</v>
+        <v>707207</v>
       </c>
       <c r="R51" t="n">
-        <v>6635740</v>
+        <v>6635607</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6602,22 +5983,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6626,72 +5997,71 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112801678</v>
+        <v>113024364</v>
       </c>
       <c r="B52" t="n">
-        <v>91220</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ekalund (Ekalund), Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707208</v>
+        <v>707080</v>
       </c>
       <c r="R52" t="n">
-        <v>6635530</v>
+        <v>6635593</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6715,22 +6085,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6745,68 +6105,64 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112813338</v>
+        <v>113024365</v>
       </c>
       <c r="B53" t="n">
-        <v>89487</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5747</v>
+        <v>5966</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707219</v>
+        <v>707115</v>
       </c>
       <c r="R53" t="n">
-        <v>6635565</v>
+        <v>6635591</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6830,27 +6186,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Luktar starkt "skoaffär". Växte intill grov gran.</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6859,34 +6200,32 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113024358</v>
+        <v>82169853</v>
       </c>
       <c r="B54" t="n">
-        <v>86426</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6894,37 +6233,40 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1988</v>
+        <v>6439</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707081</v>
+        <v>707322</v>
       </c>
       <c r="R54" t="n">
-        <v>6635696</v>
+        <v>6635990</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6948,12 +6290,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6962,37 +6309,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113024356</v>
+        <v>82169931</v>
       </c>
       <c r="B55" t="n">
-        <v>90141</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7000,37 +6339,40 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>937</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707016</v>
+        <v>707383</v>
       </c>
       <c r="R55" t="n">
-        <v>6635832</v>
+        <v>6636007</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7054,17 +6396,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>på granlåga. kollekt taget</t>
+          <t>På gammal tallstubbe.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7073,75 +6415,75 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113024364</v>
+        <v>82169643</v>
       </c>
       <c r="B56" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707080</v>
+        <v>707161</v>
       </c>
       <c r="R56" t="n">
-        <v>6635593</v>
+        <v>6636002</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7165,12 +6507,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7185,31 +6527,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113024361</v>
+        <v>132243945</v>
       </c>
       <c r="B57" t="n">
-        <v>91879</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7217,37 +6550,45 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707207</v>
+        <v>707094</v>
       </c>
       <c r="R57" t="n">
-        <v>6635607</v>
+        <v>6635643</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7271,12 +6612,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7285,76 +6641,95 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>113024365</v>
+        <v>82169652</v>
       </c>
       <c r="B58" t="n">
-        <v>91881</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707115</v>
+        <v>707161</v>
       </c>
       <c r="R58" t="n">
-        <v>6635591</v>
+        <v>6636002</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7378,12 +6753,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Gnagspår på torrgran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7392,75 +6772,76 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113024359</v>
+        <v>82169771</v>
       </c>
       <c r="B59" t="n">
-        <v>104341</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>340</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707086</v>
+        <v>707269</v>
       </c>
       <c r="R59" t="n">
-        <v>6635689</v>
+        <v>6635917</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7484,17 +6865,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>minst 9 plantor</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7503,82 +6879,72 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125656453</v>
+        <v>132216358</v>
       </c>
       <c r="B60" t="n">
-        <v>58073</v>
+        <v>5181</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Skrattsjön SV, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707472</v>
+        <v>707052</v>
       </c>
       <c r="R60" t="n">
-        <v>6636313</v>
+        <v>6635680</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7602,17 +6968,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Matar ungar ca 200 m V</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7627,60 +6988,69 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Eriksson</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Eriksson</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131431280</v>
+        <v>82169826</v>
       </c>
       <c r="B61" t="n">
-        <v>75293</v>
+        <v>5471</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1114</v>
+        <v>101377</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelekslav</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lecanographa amylacea</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ehrh. ex Pers.) Egea &amp; Torrente</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Haggård, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707019</v>
+        <v>707322</v>
       </c>
       <c r="R61" t="n">
-        <v>6635839</v>
+        <v>6635990</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7704,12 +7074,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Gnagspår på högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7718,32 +7093,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Värdefull natur i Stockholms län</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131431278</v>
+        <v>82169409</v>
       </c>
       <c r="B62" t="n">
-        <v>91903</v>
+        <v>4872</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7751,37 +7123,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5321</v>
+        <v>101675</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Geoffroy, 1785)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Haggård, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707150</v>
+        <v>707123</v>
       </c>
       <c r="R62" t="n">
-        <v>6636054</v>
+        <v>6635931</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7805,12 +7186,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Gnagspår på högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7826,26 +7212,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Värdefull natur i Stockholms län</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132218114</v>
+        <v>82169013</v>
       </c>
       <c r="B63" t="n">
-        <v>84151</v>
+        <v>4781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7853,37 +7235,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1444</v>
+        <v>102306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707052</v>
+        <v>707090</v>
       </c>
       <c r="R63" t="n">
-        <v>6635913</v>
+        <v>6635941</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7907,12 +7298,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7921,28 +7312,29 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132218069</v>
+        <v>82169550</v>
       </c>
       <c r="B64" t="n">
-        <v>97987</v>
+        <v>4781</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7950,37 +7342,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707184</v>
+        <v>707170</v>
       </c>
       <c r="R64" t="n">
-        <v>6635847</v>
+        <v>6635990</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8004,12 +7405,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8018,28 +7419,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132214935</v>
+        <v>82169571</v>
       </c>
       <c r="B65" t="n">
-        <v>92337</v>
+        <v>4781</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8047,37 +7449,46 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4217</v>
+        <v>102306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>707044</v>
+        <v>707199</v>
       </c>
       <c r="R65" t="n">
-        <v>6635846</v>
+        <v>6635984</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8101,12 +7512,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8115,43 +7526,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132216358</v>
+        <v>82169734</v>
       </c>
       <c r="B66" t="n">
-        <v>5179</v>
+        <v>4781</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8159,42 +7556,46 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707052</v>
+        <v>707226</v>
       </c>
       <c r="R66" t="n">
-        <v>6635680</v>
+        <v>6635935</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8218,12 +7619,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8232,61 +7633,76 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132214236</v>
+        <v>132243952</v>
       </c>
       <c r="B67" t="n">
-        <v>80659</v>
+        <v>58519</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228430</v>
+        <v>102990</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>706939</v>
+        <v>707009</v>
       </c>
       <c r="R67" t="n">
-        <v>6635897</v>
+        <v>6635864</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8313,11 +7729,21 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8326,26 +7752,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132227423</v>
+        <v>132243953</v>
       </c>
       <c r="B68" t="n">
-        <v>96430</v>
+        <v>58349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8353,37 +7784,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707098</v>
+        <v>707009</v>
       </c>
       <c r="R68" t="n">
-        <v>6635735</v>
+        <v>6635864</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8410,11 +7850,21 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8423,26 +7873,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132214790</v>
+        <v>82169778</v>
       </c>
       <c r="B69" t="n">
-        <v>91970</v>
+        <v>5199</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8450,37 +7905,46 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5321</v>
+        <v>105930</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707028</v>
+        <v>707269</v>
       </c>
       <c r="R69" t="n">
-        <v>6635854</v>
+        <v>6635917</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8504,12 +7968,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8518,50 +7982,51 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132216648</v>
+        <v>132216402</v>
       </c>
       <c r="B70" t="n">
-        <v>91934</v>
+        <v>107690</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5442</v>
+        <v>219686</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8571,10 +8036,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707065</v>
+        <v>707053</v>
       </c>
       <c r="R70" t="n">
-        <v>6635643</v>
+        <v>6635668</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8633,10 +8098,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132222629</v>
+        <v>132215849</v>
       </c>
       <c r="B71" t="n">
-        <v>106248</v>
+        <v>99218</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8644,49 +8109,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>219862</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707139</v>
+        <v>707074</v>
       </c>
       <c r="R71" t="n">
-        <v>6635834</v>
+        <v>6635682</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8718,40 +8171,34 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>C:a 10 exemplar.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132215849</v>
+        <v>132227426</v>
       </c>
       <c r="B72" t="n">
-        <v>99145</v>
+        <v>99218</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8779,14 +8226,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>707074</v>
+        <v>707352</v>
       </c>
       <c r="R72" t="n">
-        <v>6635682</v>
+        <v>6635802</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8833,22 +8280,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132227426</v>
+        <v>132243950</v>
       </c>
       <c r="B73" t="n">
-        <v>99145</v>
+        <v>99218</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8873,20 +8320,34 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707352</v>
+        <v>707098</v>
       </c>
       <c r="R73" t="n">
-        <v>6635802</v>
+        <v>6635691</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8913,11 +8374,21 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -8926,26 +8397,31 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132222660</v>
+        <v>132222629</v>
       </c>
       <c r="B74" t="n">
-        <v>106248</v>
+        <v>106324</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8970,21 +8446,13 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
@@ -8997,10 +8465,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707127</v>
+        <v>707139</v>
       </c>
       <c r="R74" t="n">
-        <v>6635639</v>
+        <v>6635834</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9037,7 +8505,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>C:a 10 ex.</t>
+          <t>C:a 10 exemplar.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9065,10 +8533,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132227420</v>
+        <v>132222660</v>
       </c>
       <c r="B75" t="n">
-        <v>80394</v>
+        <v>106324</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9076,37 +8544,57 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>221144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>707005</v>
+        <v>707127</v>
       </c>
       <c r="R75" t="n">
-        <v>6635885</v>
+        <v>6635639</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9138,34 +8626,40 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132216402</v>
+        <v>132214164</v>
       </c>
       <c r="B76" t="n">
-        <v>107613</v>
+        <v>106679</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9173,34 +8667,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219686</v>
+        <v>221570</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Mörk lungört</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Pulmonaria obscura</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Dumort.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>707053</v>
+        <v>706914</v>
       </c>
       <c r="R76" t="n">
-        <v>6635668</v>
+        <v>6635923</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9259,48 +8753,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132227427</v>
+        <v>132218069</v>
       </c>
       <c r="B77" t="n">
-        <v>92644</v>
+        <v>98060</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>757</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707230</v>
+        <v>707184</v>
       </c>
       <c r="R77" t="n">
-        <v>6635950</v>
+        <v>6635847</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9330,11 +8824,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Tallåga, solexponerad</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9349,22 +8838,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132217832</v>
+        <v>132214156</v>
       </c>
       <c r="B78" t="n">
-        <v>91876</v>
+        <v>104707</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9372,37 +8861,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>222412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707382</v>
+        <v>706914</v>
       </c>
       <c r="R78" t="n">
-        <v>6635863</v>
+        <v>6635923</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9451,17 +8940,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktor Lund, Gabriel Ekman, Joakim Ekman, Martin Westberg, Cajsa Björkén</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132243950</v>
+        <v>132227419</v>
       </c>
       <c r="B79" t="n">
-        <v>99145</v>
+        <v>104707</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9469,51 +8958,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219862</v>
+        <v>222412</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>707098</v>
+        <v>706917</v>
       </c>
       <c r="R79" t="n">
-        <v>6635691</v>
+        <v>6635908</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9540,21 +9015,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9563,78 +9028,59 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132243953</v>
+        <v>132214236</v>
       </c>
       <c r="B80" t="n">
-        <v>58328</v>
+        <v>80703</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>707009</v>
+        <v>706939</v>
       </c>
       <c r="R80" t="n">
-        <v>6635864</v>
+        <v>6635897</v>
       </c>
       <c r="S80" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9661,21 +9107,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9684,69 +9120,59 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132243956</v>
+        <v>132218153</v>
       </c>
       <c r="B81" t="n">
-        <v>79839</v>
+        <v>80703</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1026</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Ädellav</t>
-        </is>
+        <v>228430</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Megalaria grossa</t>
+          <t>Blastenia relicta</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pers. ex Nyl.) Hafellner</t>
+          <t>Arup &amp; Vondrák</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>707009</v>
+        <v>707015</v>
       </c>
       <c r="R81" t="n">
-        <v>6635864</v>
+        <v>6635968</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9773,21 +9199,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9796,21 +9212,16 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9820,11 +9231,11 @@
         <v>132243957</v>
       </c>
       <c r="B82" t="n">
-        <v>80659</v>
+        <v>80703</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -9953,56 +9364,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132243945</v>
+        <v>132227420</v>
       </c>
       <c r="B83" t="n">
-        <v>57951</v>
+        <v>80438</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>707094</v>
+        <v>707005</v>
       </c>
       <c r="R83" t="n">
-        <v>6635643</v>
+        <v>6635885</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10029,26 +9432,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10057,97 +9445,61 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132243949</v>
+        <v>132243955</v>
       </c>
       <c r="B84" t="n">
-        <v>106209</v>
+        <v>80438</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>340</v>
+        <v>229497</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>707078</v>
+        <v>707009</v>
       </c>
       <c r="R84" t="n">
-        <v>6635703</v>
+        <v>6635864</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10198,13 +9550,12 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Blockig, gles blandskog</t>
+          <t>Barrblandskog, luckig</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10222,10 +9573,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132243955</v>
+        <v>82170031</v>
       </c>
       <c r="B85" t="n">
-        <v>80394</v>
+        <v>96437</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10233,34 +9584,38 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229497</v>
+        <v>2667</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>707009</v>
+        <v>707494</v>
       </c>
       <c r="R85" t="n">
-        <v>6635864</v>
+        <v>6636268</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10287,22 +9642,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>På gammal asp.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10311,80 +9661,70 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132243952</v>
+        <v>82170167</v>
       </c>
       <c r="B86" t="n">
-        <v>58498</v>
+        <v>93197</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102990</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>707009</v>
+        <v>707527</v>
       </c>
       <c r="R86" t="n">
-        <v>6635864</v>
+        <v>6636021</v>
       </c>
       <c r="S86" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10408,22 +9748,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10432,26 +9762,461 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>73253961</v>
+      </c>
+      <c r="B87" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Skrattsjön, S om, Estuna, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>707542</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6636370</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2018-09-23</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2018-09-23</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog, invid mindre stig. Medobs Edvin Stighäll.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>82257673</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>707522</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6635935</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>125656453</v>
+      </c>
+      <c r="B89" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Skrattsjön SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>707472</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6636313</v>
+      </c>
+      <c r="S89" t="n">
+        <v>25</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Matar ungar ca 200 m V</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Eriksson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Eriksson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>82170052</v>
+      </c>
+      <c r="B90" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>707513</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6636298</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169679</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169838</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113024359</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113409392</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243949</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132227427</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113024356</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1541,6 +1581,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132216534</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243956</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431280</t>
         </is>
       </c>
     </row>
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82257772</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1973,6 +2033,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73253922</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2152,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82257888</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2201,6 +2271,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82258548</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,6 +2390,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82258553</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2423,6 +2503,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801374</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2520,6 +2605,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132218114</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2628,6 +2718,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801254</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2729,6 +2824,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113024358</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2837,6 +2937,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112798700</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2939,6 +3044,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169978</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3046,6 +3156,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82170031</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3143,6 +3258,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132227423</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3251,6 +3371,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801334</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3359,6 +3484,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801408</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3467,6 +3597,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112800970</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3573,6 +3708,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169956</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3685,6 +3825,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214935</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3793,6 +3938,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112800547</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3901,6 +4051,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801723</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4002,6 +4157,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82170167</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4115,6 +4275,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73253943</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4228,6 +4393,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73253961</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4336,6 +4506,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801234</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4444,6 +4619,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801348</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4552,6 +4732,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801220</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4660,6 +4845,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801302</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4762,6 +4952,11 @@
           <t>Värdefull natur i Stockholms län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131431278</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4859,6 +5054,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214790</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4960,6 +5160,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82257709</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5057,6 +5262,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132216648</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5163,6 +5373,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169875</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5269,6 +5484,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82257673</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5375,6 +5595,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82257697</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5472,6 +5697,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132217832</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5588,6 +5818,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112813338</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73253929</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5802,6 +6042,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169803</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5910,6 +6155,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112798925</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6018,6 +6268,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112800935</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6126,6 +6381,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112800985</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6234,6 +6494,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801385</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6342,6 +6607,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112801678</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6444,6 +6714,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113024361</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6545,6 +6820,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113024364</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6644,6 +6924,11 @@
       <c r="AY57" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113024365</t>
         </is>
       </c>
     </row>
@@ -6752,6 +7037,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169853</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6858,6 +7148,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169931</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6963,6 +7258,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169643</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7103,6 +7403,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243945</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7215,6 +7520,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169652</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7322,6 +7632,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169771</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7424,6 +7739,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132216358</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7536,6 +7856,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169826</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7648,6 +7973,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169409</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7755,6 +8085,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169013</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7862,6 +8197,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169550</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7969,6 +8309,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169571</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8076,6 +8421,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169734</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8197,6 +8547,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243952</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8318,6 +8673,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243953</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8436,6 +8796,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125656453</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8543,6 +8908,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82169778</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8640,6 +9010,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132216402</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8737,6 +9112,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132215849</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8834,6 +9214,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132227426</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8960,6 +9345,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243950</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9075,6 +9465,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132222629</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9198,6 +9593,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132222660</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9295,6 +9695,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214164</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9392,6 +9797,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132218069</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9489,6 +9899,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214156</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9586,6 +10001,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132227419</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9688,6 +10108,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82170052</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9780,6 +10205,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214236</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9872,6 +10302,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132218153</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10008,6 +10443,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243957</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10105,6 +10545,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132227420</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10217,8 +10662,104 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243955</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>